--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="239">
   <si>
     <t>No</t>
   </si>
@@ -56,13 +56,10 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>OT01: BTC 1m Minimal Hour</t>
   </si>
   <si>
-    <t>https://uat-api.3ona.co/exchange/v1/public/get-candlestick</t>
+    <t>/public/get-candlestick</t>
   </si>
   <si>
     <t>GET</t>
@@ -86,9 +83,6 @@
     <t>Get candlestick data from exchange API</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
     <t>OT02: BTC 1h Medium Day</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
 }</t>
   </si>
   <si>
-    <t>003</t>
-  </si>
-  <si>
     <t>OT03: BTC 1D Large Month</t>
   </si>
   <si>
@@ -122,9 +113,6 @@
 }</t>
   </si>
   <si>
-    <t>004</t>
-  </si>
-  <si>
     <t>OT04: ETH 1m Medium Month</t>
   </si>
   <si>
@@ -140,9 +128,6 @@
 }</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>OT05: ETH 1h Large Hour</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
 }</t>
   </si>
   <si>
-    <t>006</t>
-  </si>
-  <si>
     <t>OT06: ETH 1D Small Day</t>
   </si>
   <si>
@@ -176,9 +158,6 @@
 }</t>
   </si>
   <si>
-    <t>007</t>
-  </si>
-  <si>
     <t>OT07: XRP 1m Large Day</t>
   </si>
   <si>
@@ -194,9 +173,6 @@
 }</t>
   </si>
   <si>
-    <t>008</t>
-  </si>
-  <si>
     <t>OT08: XRP 1h Small Month</t>
   </si>
   <si>
@@ -212,9 +188,6 @@
 }</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
     <t>OT09: XRP 1D Medium Hour</t>
   </si>
   <si>
@@ -230,9 +203,6 @@
 }</t>
   </si>
   <si>
-    <t>010</t>
-  </si>
-  <si>
     <t>SP01: 5min Common Trading</t>
   </si>
   <si>
@@ -248,9 +218,6 @@
 }</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>SP02: 15min Standard</t>
   </si>
   <si>
@@ -266,9 +233,6 @@
 }</t>
   </si>
   <si>
-    <t>012</t>
-  </si>
-  <si>
     <t>SP03: 30min Half Hour</t>
   </si>
   <si>
@@ -284,9 +248,6 @@
 }</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>SP04: 2h Two Hours</t>
   </si>
   <si>
@@ -302,9 +263,6 @@
 }</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>SP05: 4h Important Swing</t>
   </si>
   <si>
@@ -320,9 +278,6 @@
 }</t>
   </si>
   <si>
-    <t>015</t>
-  </si>
-  <si>
     <t>SP06: 12h Half Day</t>
   </si>
   <si>
@@ -338,9 +293,6 @@
 }</t>
   </si>
   <si>
-    <t>016</t>
-  </si>
-  <si>
     <t>SP07: 7D Weekly</t>
   </si>
   <si>
@@ -356,9 +308,6 @@
 }</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>SP08: 14D Bi-weekly</t>
   </si>
   <si>
@@ -374,9 +323,6 @@
 }</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>SP09: 1M Monthly</t>
   </si>
   <si>
@@ -392,9 +338,6 @@
 }</t>
   </si>
   <si>
-    <t>019</t>
-  </si>
-  <si>
     <t>SP10: 5min Performance</t>
   </si>
   <si>
@@ -410,9 +353,6 @@
 }</t>
   </si>
   <si>
-    <t>020</t>
-  </si>
-  <si>
     <t>NT01: Invalid Instrument</t>
   </si>
   <si>
@@ -428,9 +368,6 @@
     <t>Get candlestick data with invalid/missing parameters</t>
   </si>
   <si>
-    <t>021</t>
-  </si>
-  <si>
     <t>NT02: Invalid Timeframe</t>
   </si>
   <si>
@@ -443,9 +380,6 @@
 }</t>
   </si>
   <si>
-    <t>022</t>
-  </si>
-  <si>
     <t>NT03: Negative Count</t>
   </si>
   <si>
@@ -458,9 +392,6 @@
 }</t>
   </si>
   <si>
-    <t>023</t>
-  </si>
-  <si>
     <t>NT04: Excessive Count</t>
   </si>
   <si>
@@ -473,18 +404,12 @@
 }</t>
   </si>
   <si>
-    <t>024</t>
-  </si>
-  <si>
     <t>NT05: Case Sensitive</t>
   </si>
   <si>
     <t>{"count": "100", "timeframe": "1H", "instrument_name": "btc_usd"}</t>
   </si>
   <si>
-    <t>025</t>
-  </si>
-  <si>
     <t>Minimum timeframe - 1m</t>
   </si>
   <si>
@@ -492,9 +417,6 @@
   </si>
   <si>
     <t>Get candlestick data - edge case scenarios</t>
-  </si>
-  <si>
-    <t>026</t>
   </si>
   <si>
     <t>Maximum timeframe - 1M</t>
@@ -512,25 +434,16 @@
 }</t>
   </si>
   <si>
-    <t>027</t>
-  </si>
-  <si>
     <t>Maximum count - 5000</t>
   </si>
   <si>
     <t>{"count": "5000", "timeframe": "1m", "instrument_name": "ETH_USD"}</t>
   </si>
   <si>
-    <t>028</t>
-  </si>
-  <si>
     <t>Case sensitive - lowercase</t>
   </si>
   <si>
     <t>{"count": "10", "timeframe": "1h", "instrument_name": "btc_usd"}</t>
-  </si>
-  <si>
-    <t>029</t>
   </si>
   <si>
     <t>Different pair - BTC_USDT</t>
@@ -548,25 +461,379 @@
 }</t>
   </si>
   <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>Medium timeframe - 1h</t>
   </si>
   <si>
     <t>{"count": "500", "timeframe": "1h", "instrument_name": "ETH_USD"}</t>
   </si>
   <si>
-    <t>031</t>
-  </si>
-  <si>
     <t>Decimal count - 100.5</t>
   </si>
   <si>
     <t>{"count": "100", "timeframe": "1D", "instrument_name": "ETH_USD"}</t>
   </si>
   <si>
-    <t>032</t>
+    <t>TS01: Only start_ts - Last 24 hours</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1760314836330"}</t>
+  </si>
+  <si>
+    <t>Retrieve data from 24 hours ago to now using start_ts</t>
+  </si>
+  <si>
+    <t>TS02: Only end_ts - Until 1 hour ago</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "end_ts": "1760397636330"}</t>
+  </si>
+  <si>
+    <t>Retrieve data until 1 hour ago using end_ts</t>
+  </si>
+  <si>
+    <t>TS03: Both start_ts and end_ts - 1 week range</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1759796436330", "end_ts": "1760401236330"}</t>
+  </si>
+  <si>
+    <t>Retrieve data for specific time range (1 week)</t>
+  </si>
+  <si>
+    <t>TS04: Short time range - 1 hour</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1m", "start_ts": "1760397636330", "end_ts": "1760401236330"}</t>
+  </si>
+  <si>
+    <t>Test short time range with 1-minute interval</t>
+  </si>
+  <si>
+    <t>TS05: Long time range - 1 month</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1D", "start_ts": "1757809236330", "end_ts": "1760401236330"}</t>
+  </si>
+  <si>
+    <t>Test long time range with daily interval</t>
+  </si>
+  <si>
+    <t>TS06: start_ts with count</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1759796436330", "count": "100"}</t>
+  </si>
+  <si>
+    <t>Test start_ts combined with count parameter</t>
+  </si>
+  <si>
+    <t>TS07: end_ts with count</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "end_ts": "1760401236330", "count": "50"}</t>
+  </si>
+  <si>
+    <t>Test end_ts combined with count parameter</t>
+  </si>
+  <si>
+    <t>TS08: start_ts, end_ts and count</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1759796436330", "end_ts": "1760401236330", "count": "100"}</t>
+  </si>
+  <si>
+    <t>Test all time parameters together - check priority</t>
+  </si>
+  <si>
+    <t>TS09: start_ts equals end_ts</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1760397636330", "end_ts": "1760397636330"}</t>
+  </si>
+  <si>
+    <t>Boundary test: start_ts equals end_ts (single point)</t>
+  </si>
+  <si>
+    <t>TS10: Very old start_ts - 1 year ago</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1D", "start_ts": "1728865236330", "count": "100"}</t>
+  </si>
+  <si>
+    <t>Test with very old timestamp (1 year ago)</t>
+  </si>
+  <si>
+    <t>TS11: Different instruments with timestamps</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "ETH_USD", "timeframe": "4h", "start_ts": "1759796436330", "end_ts": "1760401236330"}</t>
+  </si>
+  <si>
+    <t>Test timestamps with different trading pair</t>
+  </si>
+  <si>
+    <t>TS-N01: start_ts &gt; end_ts (inverted)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1760401236330", "end_ts": "1759796436330"}</t>
+  </si>
+  <si>
+    <t>{
+  "code": 10004,
+  "msg": "Invalid parameter"
+}</t>
+  </si>
+  <si>
+    <t>Negative: start_ts is after end_ts (invalid time range)</t>
+  </si>
+  <si>
+    <t>TS-N02: Future end_ts</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "end_ts": "1760404836330"}</t>
+  </si>
+  <si>
+    <t>Negative: end_ts is in the future</t>
+  </si>
+  <si>
+    <t>TS-N03: Invalid start_ts - negative value</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "-1000"}</t>
+  </si>
+  <si>
+    <t>Negative: start_ts with negative value</t>
+  </si>
+  <si>
+    <t>TS-N04: Invalid start_ts - zero</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "0"}</t>
+  </si>
+  <si>
+    <t>Negative: start_ts with zero value</t>
+  </si>
+  <si>
+    <t>TS-N05: Invalid start_ts - non-numeric</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "invalid_timestamp"}</t>
+  </si>
+  <si>
+    <t>Negative: start_ts with non-numeric string</t>
+  </si>
+  <si>
+    <t>TS-N06: Invalid end_ts - non-numeric</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "end_ts": "abc123"}</t>
+  </si>
+  <si>
+    <t>Negative: end_ts with non-numeric string</t>
+  </si>
+  <si>
+    <t>TS-N07: Extremely large timestamp</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "9999999999999"}</t>
+  </si>
+  <si>
+    <t>Negative: start_ts with extremely large value (year 2286)</t>
+  </si>
+  <si>
+    <t>TS-N08: Milliseconds vs Seconds confusion</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1760314836"}</t>
+  </si>
+  <si>
+    <t>Negative: Using seconds instead of milliseconds (if API expects milliseconds)</t>
+  </si>
+  <si>
+    <t>DV01: Only required param - Use all defaults</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD"}</t>
+  </si>
+  <si>
+    <t>Test API defaults: timeframe=M1, count=25, start_ts=1day ago, end_ts=now</t>
+  </si>
+  <si>
+    <t>DV02: Only instrument + timeframe</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h"}</t>
+  </si>
+  <si>
+    <t>Default count=25, default time range (1 day ago to now)</t>
+  </si>
+  <si>
+    <t>DV03: Only instrument + count</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "count": "50"}</t>
+  </si>
+  <si>
+    <t>Default timeframe=M1, default time range (1 day ago to now)</t>
+  </si>
+  <si>
+    <t>DV04: Explicit default timeframe - M1</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "M1"}</t>
+  </si>
+  <si>
+    <t>Explicitly set timeframe=M1 (API default value) - should behave same as DV01</t>
+  </si>
+  <si>
+    <t>DV05: Explicit default count - 25</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "count": "25"}</t>
+  </si>
+  <si>
+    <t>Explicitly set count=25 (API default value) - verify data count</t>
+  </si>
+  <si>
+    <t>DV06: Explicit all defaults</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "M1", "count": "25"}</t>
+  </si>
+  <si>
+    <t>Explicitly set all optional params to default values</t>
+  </si>
+  <si>
+    <t>DV07: Verify default start_ts (1 day ago)</t>
+  </si>
+  <si>
+    <t>Verify oldest data is ~24 hours old when using default start_ts</t>
+  </si>
+  <si>
+    <t>DV08: Verify default end_ts (current time)</t>
+  </si>
+  <si>
+    <t>Verify newest data is close to current time when using default end_ts</t>
+  </si>
+  <si>
+    <t>DV09: Override default count - 100 vs 25</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "count": "100"}</t>
+  </si>
+  <si>
+    <t>Compare response with default count=25 - should return 100 records</t>
+  </si>
+  <si>
+    <t>DV10: Override default timeframe - 1D vs M1</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1D", "count": "10"}</t>
+  </si>
+  <si>
+    <t>Compare with default timeframe=M1 - interval should be 1D</t>
+  </si>
+  <si>
+    <t>DV11: Count=1 (minimum)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "count": "1"}</t>
+  </si>
+  <si>
+    <t>Minimum count with default timeframe and time range</t>
+  </si>
+  <si>
+    <t>DV12: Count=0 (edge case)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "count": "0"}</t>
+  </si>
+  <si>
+    <t>Edge case: count=0 should fail or return empty (test default behavior)</t>
+  </si>
+  <si>
+    <t>DV13: Large count with default time range</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1m", "count": "2000"}</t>
+  </si>
+  <si>
+    <t>Test if count &gt; available data in default 24h range (1440 minutes)</t>
+  </si>
+  <si>
+    <t>DV14: Small count with default time range</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "count": "5"}</t>
+  </si>
+  <si>
+    <t>Test small count (5) with default 24h range - should return latest 5 records</t>
+  </si>
+  <si>
+    <t>DV15: Defaults with ETH_USD</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "ETH_USD"}</t>
+  </si>
+  <si>
+    <t>Verify default values work consistently across different instruments</t>
+  </si>
+  <si>
+    <t>DV16: Defaults with BTC_USDT</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USDT"}</t>
+  </si>
+  <si>
+    <t>Verify default values work with stablecoin pairs</t>
+  </si>
+  <si>
+    <t>DV17: Empty timeframe string</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": ""}</t>
+  </si>
+  <si>
+    <t>Empty string vs omitted param - should fail (not use default)</t>
+  </si>
+  <si>
+    <t>DV18: Empty count string</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "count": ""}</t>
+  </si>
+  <si>
+    <t>DV19: Legacy timeframe format - M1</t>
+  </si>
+  <si>
+    <t>Test legacy format M1 (default value) still works</t>
+  </si>
+  <si>
+    <t>DV20: Modern format - 1m (same as default M1)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1m"}</t>
+  </si>
+  <si>
+    <t>Modern format 1m vs legacy M1 - should return same data</t>
+  </si>
+  <si>
+    <t>DV21: Only start_ts (omit end_ts for default)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "start_ts": "1760358674117"}</t>
+  </si>
+  <si>
+    <t>Custom start_ts + default end_ts (current time)</t>
+  </si>
+  <si>
+    <t>DV22: Only end_ts (omit start_ts for default)</t>
+  </si>
+  <si>
+    <t>{"instrument_name": "BTC_USD", "timeframe": "1h", "end_ts": "1760358674117"}</t>
+  </si>
+  <si>
+    <t>Default start_ts (1 day ago) + custom end_ts</t>
   </si>
   <si>
     <t>Invalid channel - random string</t>
@@ -587,67 +854,34 @@
     <t>Connect to WebSocket server</t>
   </si>
   <si>
-    <t>033</t>
-  </si>
-  <si>
     <t>Invalid channel - wrong type</t>
   </si>
   <si>
-    <t>034</t>
-  </si>
-  <si>
     <t>Invalid channel - empty string</t>
   </si>
   <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>Invalid instrument - does not exist</t>
   </si>
   <si>
-    <t>036</t>
-  </si>
-  <si>
     <t>Invalid instrument - missing suffix</t>
   </si>
   <si>
-    <t>037</t>
-  </si>
-  <si>
     <t>Invalid instrument - lowercase</t>
   </si>
   <si>
-    <t>038</t>
-  </si>
-  <si>
     <t>Invalid instrument - special characters</t>
   </si>
   <si>
-    <t>039</t>
-  </si>
-  <si>
     <t>Malformed - missing method field</t>
   </si>
   <si>
-    <t>040</t>
-  </si>
-  <si>
     <t>Malformed - missing params field</t>
   </si>
   <si>
-    <t>041</t>
-  </si>
-  <si>
     <t>Malformed - invalid method name</t>
   </si>
   <si>
-    <t>042</t>
-  </si>
-  <si>
     <t>Subscribe to BTCUSD-PERP ticker</t>
-  </si>
-  <si>
-    <t>043</t>
   </si>
   <si>
     <t>Subscribe to ETHUSD-PERP ticker</t>
@@ -674,7 +908,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -831,18 +1064,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1031,12 +1258,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1161,7 +1403,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1173,128 +1415,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1649,18 +1885,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="52.2403846153846" customWidth="1"/>
-    <col min="3" max="3" width="31.5673076923077" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="24.3653846153846" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="45" customWidth="1"/>
+    <col min="1" max="1" width="4.46153846153846" customWidth="1"/>
+    <col min="2" max="2" width="58.0096153846154" customWidth="1"/>
+    <col min="3" max="3" width="26.9134615384615" customWidth="1"/>
+    <col min="4" max="4" width="8.53846153846154" customWidth="1"/>
+    <col min="5" max="5" width="37.9230769230769" customWidth="1"/>
+    <col min="6" max="6" width="124.615384615385" customWidth="1"/>
+    <col min="7" max="7" width="14.9230769230769" customWidth="1"/>
+    <col min="8" max="8" width="81.8461538461538" customWidth="1"/>
+    <col min="9" max="9" width="79.5384615384615" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1692,1251 +1928,2440 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="118" spans="1:9">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2">
-        <v>200</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="118" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>200</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>200</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>200</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9">
+        <v>200</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10">
+        <v>200</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11">
+        <v>200</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
+        <v>200</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13">
+        <v>200</v>
+      </c>
+      <c r="H13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>200</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>200</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16">
+        <v>200</v>
+      </c>
+      <c r="H16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17">
+        <v>200</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18">
+        <v>200</v>
+      </c>
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>200</v>
+      </c>
+      <c r="H19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="G3" s="2">
-        <v>200</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20">
+        <v>200</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="118" spans="1:9">
-      <c r="A4" s="3" t="s">
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21">
+        <v>400</v>
+      </c>
+      <c r="H21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>400</v>
+      </c>
+      <c r="H22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23">
+        <v>400</v>
+      </c>
+      <c r="H23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="G4" s="2">
-        <v>200</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24">
+        <v>200</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="118" spans="1:9">
-      <c r="A5" s="3" t="s">
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25">
+        <v>400</v>
+      </c>
+      <c r="H25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26">
+        <v>200</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27">
+        <v>200</v>
+      </c>
+      <c r="H27" t="s">
+        <v>90</v>
+      </c>
+      <c r="I27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="G5" s="2">
-        <v>200</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28">
+        <v>200</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="118" spans="1:9">
-      <c r="A6" s="3" t="s">
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29">
+        <v>400</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30">
+        <v>200</v>
+      </c>
+      <c r="H30" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31">
+        <v>200</v>
+      </c>
+      <c r="H31" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="G6" s="2">
-        <v>200</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32">
+        <v>200</v>
+      </c>
+      <c r="H32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="118" spans="1:9">
-      <c r="A7" s="3" t="s">
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33">
+        <v>200</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34">
+        <v>200</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35">
+        <v>200</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="G7" s="2">
-        <v>200</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36">
+        <v>200</v>
+      </c>
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="118" spans="1:9">
-      <c r="A8" s="3" t="s">
+      <c r="B37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37">
+        <v>200</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38">
+        <v>200</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39">
+        <v>200</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="G8" s="2">
-        <v>200</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40">
+        <v>200</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="118" spans="1:9">
-      <c r="A9" s="3" t="s">
+      <c r="B41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="B43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="G9" s="2">
-        <v>200</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44">
+        <v>400</v>
+      </c>
+      <c r="H44" t="s">
+        <v>137</v>
+      </c>
+      <c r="I44" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="118" spans="1:9">
-      <c r="A10" s="3" t="s">
+      <c r="B45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45">
+        <v>400</v>
+      </c>
+      <c r="H45" t="s">
+        <v>137</v>
+      </c>
+      <c r="I45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46">
+        <v>400</v>
+      </c>
+      <c r="H46" t="s">
+        <v>137</v>
+      </c>
+      <c r="I46" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="B47" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>146</v>
+      </c>
+      <c r="G47">
+        <v>400</v>
+      </c>
+      <c r="H47" t="s">
+        <v>137</v>
+      </c>
+      <c r="I47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="G10" s="2">
-        <v>200</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="B48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48">
+        <v>400</v>
+      </c>
+      <c r="H48" t="s">
+        <v>137</v>
+      </c>
+      <c r="I48" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" ht="118" spans="1:9">
-      <c r="A11" s="2" t="s">
+      <c r="B49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49">
+        <v>400</v>
+      </c>
+      <c r="H49" t="s">
+        <v>137</v>
+      </c>
+      <c r="I49" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B50" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>155</v>
+      </c>
+      <c r="G50">
+        <v>400</v>
+      </c>
+      <c r="H50" t="s">
+        <v>137</v>
+      </c>
+      <c r="I50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="B51" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51">
+        <v>400</v>
+      </c>
+      <c r="H51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="G11" s="2">
-        <v>200</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="B52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>161</v>
+      </c>
+      <c r="G52">
+        <v>200</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" ht="118" spans="1:9">
-      <c r="A12" s="2" t="s">
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>164</v>
+      </c>
+      <c r="G53">
+        <v>200</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>167</v>
+      </c>
+      <c r="G54">
+        <v>200</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="B55" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55">
+        <v>200</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="G12" s="2">
-        <v>200</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="B56" t="s">
+        <v>172</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>173</v>
+      </c>
+      <c r="G56">
+        <v>200</v>
+      </c>
+      <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="118" spans="1:9">
-      <c r="A13" s="2" t="s">
+      <c r="B57" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>176</v>
+      </c>
+      <c r="G57">
+        <v>200</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58">
         <v>57</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B58" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>164</v>
+      </c>
+      <c r="G58">
+        <v>200</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="B59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>164</v>
+      </c>
+      <c r="G59">
+        <v>200</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="G13" s="2">
-        <v>200</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="B60" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>183</v>
+      </c>
+      <c r="G60">
+        <v>200</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" ht="118" spans="1:9">
-      <c r="A14" s="2" t="s">
+      <c r="B61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>186</v>
+      </c>
+      <c r="G61">
+        <v>200</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
         <v>61</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" t="s">
+        <v>189</v>
+      </c>
+      <c r="G62">
+        <v>200</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="B63" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>192</v>
+      </c>
+      <c r="G63">
+        <v>400</v>
+      </c>
+      <c r="H63" t="s">
+        <v>137</v>
+      </c>
+      <c r="I63" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="G14" s="2">
-        <v>200</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="B64" t="s">
+        <v>194</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>195</v>
+      </c>
+      <c r="G64">
+        <v>200</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" ht="118" spans="1:9">
-      <c r="A15" s="2" t="s">
+      <c r="B65" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>198</v>
+      </c>
+      <c r="G65">
+        <v>200</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B66" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>201</v>
+      </c>
+      <c r="G66">
+        <v>200</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="B67" t="s">
+        <v>203</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>204</v>
+      </c>
+      <c r="G67">
+        <v>200</v>
+      </c>
+      <c r="H67" t="s">
+        <v>33</v>
+      </c>
+      <c r="I67" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
         <v>67</v>
       </c>
-      <c r="G15" s="2">
-        <v>200</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="B68" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" t="s">
+        <v>207</v>
+      </c>
+      <c r="G68">
+        <v>400</v>
+      </c>
+      <c r="H68" t="s">
+        <v>137</v>
+      </c>
+      <c r="I68" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="118" spans="1:9">
-      <c r="A16" s="2" t="s">
+      <c r="B69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>210</v>
+      </c>
+      <c r="G69">
+        <v>400</v>
+      </c>
+      <c r="H69" t="s">
+        <v>137</v>
+      </c>
+      <c r="I69" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
         <v>69</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70">
+        <v>200</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>214</v>
+      </c>
+      <c r="G71">
+        <v>200</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72">
         <v>71</v>
       </c>
-      <c r="G16" s="2">
-        <v>200</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="B72" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>217</v>
+      </c>
+      <c r="G72">
+        <v>200</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="118" spans="1:9">
-      <c r="A17" s="2" t="s">
+      <c r="B73" t="s">
+        <v>219</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>220</v>
+      </c>
+      <c r="G73">
+        <v>200</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74">
         <v>73</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B74" t="s">
+        <v>222</v>
+      </c>
+      <c r="C74" t="s">
+        <v>223</v>
+      </c>
+      <c r="D74" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>225</v>
+      </c>
+      <c r="G74">
+        <v>200</v>
+      </c>
+      <c r="H74" t="s">
+        <v>226</v>
+      </c>
+      <c r="I74" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="B75" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" t="s">
+        <v>224</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>225</v>
+      </c>
+      <c r="G75">
+        <v>200</v>
+      </c>
+      <c r="H75" t="s">
+        <v>226</v>
+      </c>
+      <c r="I75" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="G17" s="2">
-        <v>200</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="B76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C76" t="s">
+        <v>223</v>
+      </c>
+      <c r="D76" t="s">
+        <v>224</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>225</v>
+      </c>
+      <c r="G76">
+        <v>200</v>
+      </c>
+      <c r="H76" t="s">
+        <v>226</v>
+      </c>
+      <c r="I76" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="118" spans="1:9">
-      <c r="A18" s="2" t="s">
+      <c r="B77" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" t="s">
+        <v>223</v>
+      </c>
+      <c r="D77" t="s">
+        <v>224</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>225</v>
+      </c>
+      <c r="G77">
+        <v>200</v>
+      </c>
+      <c r="H77" t="s">
+        <v>226</v>
+      </c>
+      <c r="I77" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" t="s">
+        <v>223</v>
+      </c>
+      <c r="D78" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
+        <v>225</v>
+      </c>
+      <c r="G78">
+        <v>200</v>
+      </c>
+      <c r="H78" t="s">
+        <v>226</v>
+      </c>
+      <c r="I78" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="B79" t="s">
+        <v>232</v>
+      </c>
+      <c r="C79" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" t="s">
+        <v>225</v>
+      </c>
+      <c r="G79">
+        <v>200</v>
+      </c>
+      <c r="H79" t="s">
+        <v>226</v>
+      </c>
+      <c r="I79" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="G18" s="2">
-        <v>200</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="B80" t="s">
+        <v>233</v>
+      </c>
+      <c r="C80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D80" t="s">
+        <v>224</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" t="s">
+        <v>225</v>
+      </c>
+      <c r="G80">
+        <v>200</v>
+      </c>
+      <c r="H80" t="s">
+        <v>226</v>
+      </c>
+      <c r="I80" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" ht="118" spans="1:9">
-      <c r="A19" s="2" t="s">
+      <c r="B81" t="s">
+        <v>234</v>
+      </c>
+      <c r="C81" t="s">
+        <v>223</v>
+      </c>
+      <c r="D81" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>225</v>
+      </c>
+      <c r="G81">
+        <v>200</v>
+      </c>
+      <c r="H81" t="s">
+        <v>226</v>
+      </c>
+      <c r="I81" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B82" t="s">
+        <v>235</v>
+      </c>
+      <c r="C82" t="s">
+        <v>223</v>
+      </c>
+      <c r="D82" t="s">
+        <v>224</v>
+      </c>
+      <c r="E82" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" t="s">
+        <v>225</v>
+      </c>
+      <c r="G82">
+        <v>200</v>
+      </c>
+      <c r="H82" t="s">
+        <v>226</v>
+      </c>
+      <c r="I82" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="B83" t="s">
+        <v>236</v>
+      </c>
+      <c r="C83" t="s">
+        <v>223</v>
+      </c>
+      <c r="D83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>225</v>
+      </c>
+      <c r="G83">
+        <v>200</v>
+      </c>
+      <c r="H83" t="s">
+        <v>226</v>
+      </c>
+      <c r="I83" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84">
         <v>83</v>
       </c>
-      <c r="G19" s="2">
-        <v>200</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="B84" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" t="s">
+        <v>223</v>
+      </c>
+      <c r="D84" t="s">
+        <v>224</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
+        <v>225</v>
+      </c>
+      <c r="G84">
+        <v>200</v>
+      </c>
+      <c r="H84" t="s">
+        <v>226</v>
+      </c>
+      <c r="I84" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" ht="118" spans="1:9">
-      <c r="A20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2">
-        <v>200</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="68" spans="1:9">
-      <c r="A21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="2">
-        <v>400</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" ht="68" spans="1:9">
-      <c r="A22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="2">
-        <v>400</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" ht="68" spans="1:9">
-      <c r="A23" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="2">
-        <v>400</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" ht="68" spans="1:9">
-      <c r="A24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="2">
-        <v>200</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" ht="68" spans="1:9">
-      <c r="A25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="2">
-        <v>400</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" ht="118" spans="1:9">
-      <c r="A26" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="2">
-        <v>200</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" ht="118" spans="1:9">
-      <c r="A27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" s="2">
-        <v>200</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" ht="118" spans="1:9">
-      <c r="A28" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="2">
-        <v>200</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" ht="68" spans="1:9">
-      <c r="A29" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" s="2">
-        <v>400</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" ht="118" spans="1:9">
-      <c r="A30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="2">
-        <v>200</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" ht="118" spans="1:9">
-      <c r="A31" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="2">
-        <v>200</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" ht="118" spans="1:9">
-      <c r="A32" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G32" s="2">
-        <v>200</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" ht="34" spans="1:9">
-      <c r="A33" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="2">
-        <v>200</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" ht="34" spans="1:9">
-      <c r="A34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="2">
-        <v>200</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" ht="34" spans="1:9">
-      <c r="A35" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G35" s="2">
-        <v>200</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" ht="34" spans="1:9">
-      <c r="A36" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G36" s="2">
-        <v>200</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" ht="34" spans="1:9">
-      <c r="A37" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" s="2">
-        <v>200</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" ht="34" spans="1:9">
-      <c r="A38" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G38" s="2">
-        <v>200</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" ht="34" spans="1:9">
-      <c r="A39" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G39" s="2">
-        <v>200</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" ht="34" spans="1:9">
-      <c r="A40" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G40" s="2">
-        <v>200</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" ht="34" spans="1:9">
-      <c r="A41" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G41" s="2">
-        <v>200</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" ht="34" spans="1:9">
-      <c r="A42" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G42" s="2">
-        <v>200</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" ht="51" spans="1:9">
-      <c r="A43" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="2">
-        <v>200</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" ht="34" spans="1:9">
-      <c r="A44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G44" s="2">
-        <v>200</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>139</v>
+      <c r="B85" t="s">
+        <v>238</v>
+      </c>
+      <c r="C85" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" t="s">
+        <v>225</v>
+      </c>
+      <c r="G85">
+        <v>200</v>
+      </c>
+      <c r="H85" t="s">
+        <v>226</v>
+      </c>
+      <c r="I85" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/tests/test_cases.xlsx
+++ b/tests/test_cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16500"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="REST_Candlestick" sheetId="2" r:id="rId1"/>
@@ -28,11 +28,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="504">
   <si>
     <t>Case ID</t>
   </si>
   <si>
+    <t>Jira_ID</t>
+  </si>
+  <si>
     <t>Case Name</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
     <t>001</t>
   </si>
   <si>
+    <t>TC_R001</t>
+  </si>
+  <si>
     <t>Query with only required parameters</t>
   </si>
   <si>
@@ -123,6 +129,9 @@
     <t>002</t>
   </si>
   <si>
+    <t>TC_R002</t>
+  </si>
+  <si>
     <t>Query 1-minute candlestick (timeframe=1m)</t>
   </si>
   <si>
@@ -141,6 +150,9 @@
     <t>003</t>
   </si>
   <si>
+    <t>TC_R003</t>
+  </si>
+  <si>
     <t>Query 5-minute candlestick (timeframe=5m)</t>
   </si>
   <si>
@@ -159,6 +171,9 @@
     <t>004</t>
   </si>
   <si>
+    <t>TC_R004</t>
+  </si>
+  <si>
     <t>Query 15-minute candlestick (timeframe=15m)</t>
   </si>
   <si>
@@ -174,6 +189,9 @@
     <t>005</t>
   </si>
   <si>
+    <t>TC_R005</t>
+  </si>
+  <si>
     <t>Query 1-hour candlestick (timeframe=1h)</t>
   </si>
   <si>
@@ -192,6 +210,9 @@
     <t>006</t>
   </si>
   <si>
+    <t>TC_R006</t>
+  </si>
+  <si>
     <t>Query daily candlestick (timeframe=1D)</t>
   </si>
   <si>
@@ -210,6 +231,9 @@
     <t>007</t>
   </si>
   <si>
+    <t>TC_R007</t>
+  </si>
+  <si>
     <t>Legacy format M1</t>
   </si>
   <si>
@@ -228,6 +252,9 @@
     <t>008</t>
   </si>
   <si>
+    <t>TC_R008</t>
+  </si>
+  <si>
     <t>Legacy format H1</t>
   </si>
   <si>
@@ -237,6 +264,9 @@
     <t>009</t>
   </si>
   <si>
+    <t>TC_R009</t>
+  </si>
+  <si>
     <t>Query single candlestick (count=1)</t>
   </si>
   <si>
@@ -255,6 +285,9 @@
     <t>010</t>
   </si>
   <si>
+    <t>TC_R010</t>
+  </si>
+  <si>
     <t>Query large batch (count=100)</t>
   </si>
   <si>
@@ -273,6 +306,9 @@
     <t>011</t>
   </si>
   <si>
+    <t>TC_R011</t>
+  </si>
+  <si>
     <t>Time range query with start_ts and end_ts</t>
   </si>
   <si>
@@ -291,6 +327,9 @@
     <t>012</t>
   </si>
   <si>
+    <t>TC_R012</t>
+  </si>
+  <si>
     <t>Query with only start_ts</t>
   </si>
   <si>
@@ -306,6 +345,9 @@
     <t>013</t>
   </si>
   <si>
+    <t>TC_R013</t>
+  </si>
+  <si>
     <t>Query with only end_ts</t>
   </si>
   <si>
@@ -321,6 +363,9 @@
     <t>014</t>
   </si>
   <si>
+    <t>TC_R014</t>
+  </si>
+  <si>
     <t>Verify HTTP status code 200</t>
   </si>
   <si>
@@ -339,6 +384,9 @@
     <t>015</t>
   </si>
   <si>
+    <t>TC_R015</t>
+  </si>
+  <si>
     <t>Verify business code=0</t>
   </si>
   <si>
@@ -351,6 +399,9 @@
     <t>016</t>
   </si>
   <si>
+    <t>TC_R016</t>
+  </si>
+  <si>
     <t>Verify data array length</t>
   </si>
   <si>
@@ -369,6 +420,9 @@
     <t>017</t>
   </si>
   <si>
+    <t>TC_R017</t>
+  </si>
+  <si>
     <t>Verify candlestick data format</t>
   </si>
   <si>
@@ -384,6 +438,9 @@
     <t>018</t>
   </si>
   <si>
+    <t>TC_R018</t>
+  </si>
+  <si>
     <t>Verify interval field consistency</t>
   </si>
   <si>
@@ -399,6 +456,9 @@
     <t>019</t>
   </si>
   <si>
+    <t>TC_R019</t>
+  </si>
+  <si>
     <t>Missing required parameter instrument_name</t>
   </si>
   <si>
@@ -420,6 +480,9 @@
     <t>020</t>
   </si>
   <si>
+    <t>TC_R020</t>
+  </si>
+  <si>
     <t>Invalid instrument_name</t>
   </si>
   <si>
@@ -438,6 +501,9 @@
     <t>021</t>
   </si>
   <si>
+    <t>TC_R021</t>
+  </si>
+  <si>
     <t>Non-existent trading pair ABCUSD-PERP</t>
   </si>
   <si>
@@ -450,6 +516,9 @@
     <t>022</t>
   </si>
   <si>
+    <t>TC_R022</t>
+  </si>
+  <si>
     <t>Invalid timeframe format</t>
   </si>
   <si>
@@ -462,6 +531,9 @@
     <t>023</t>
   </si>
   <si>
+    <t>TC_R023</t>
+  </si>
+  <si>
     <t>timeframe with special characters</t>
   </si>
   <si>
@@ -480,6 +552,9 @@
     <t>024</t>
   </si>
   <si>
+    <t>TC_R024</t>
+  </si>
+  <si>
     <t>count as string type</t>
   </si>
   <si>
@@ -495,6 +570,9 @@
     <t>025</t>
   </si>
   <si>
+    <t>TC_R025</t>
+  </si>
+  <si>
     <t>start_ts as string</t>
   </si>
   <si>
@@ -507,6 +585,9 @@
     <t>026</t>
   </si>
   <si>
+    <t>TC_R026</t>
+  </si>
+  <si>
     <t>end_ts as string</t>
   </si>
   <si>
@@ -516,6 +597,9 @@
     <t>027</t>
   </si>
   <si>
+    <t>TC_R027</t>
+  </si>
+  <si>
     <t>start_ts &gt; end_ts (logic error)</t>
   </si>
   <si>
@@ -531,6 +615,9 @@
     <t>028</t>
   </si>
   <si>
+    <t>TC_R028</t>
+  </si>
+  <si>
     <t>HTTP POST method instead of GET</t>
   </si>
   <si>
@@ -549,6 +636,9 @@
     <t>029</t>
   </si>
   <si>
+    <t>TC_R029</t>
+  </si>
+  <si>
     <t>URL spelling error</t>
   </si>
   <si>
@@ -567,6 +657,9 @@
     <t>030</t>
   </si>
   <si>
+    <t>TC_R030</t>
+  </si>
+  <si>
     <t>SQL injection attempt</t>
   </si>
   <si>
@@ -582,6 +675,9 @@
     <t>031</t>
   </si>
   <si>
+    <t>TC_R031</t>
+  </si>
+  <si>
     <t>count minimum value 1</t>
   </si>
   <si>
@@ -594,6 +690,9 @@
     <t>032</t>
   </si>
   <si>
+    <t>TC_R032</t>
+  </si>
+  <si>
     <t>count equals 0</t>
   </si>
   <si>
@@ -612,6 +711,9 @@
     <t>033</t>
   </si>
   <si>
+    <t>TC_R033</t>
+  </si>
+  <si>
     <t>count=-1 negative</t>
   </si>
   <si>
@@ -624,6 +726,9 @@
     <t>034</t>
   </si>
   <si>
+    <t>TC_R034</t>
+  </si>
+  <si>
     <t>count=1000 large value</t>
   </si>
   <si>
@@ -642,6 +747,9 @@
     <t>035</t>
   </si>
   <si>
+    <t>TC_R035</t>
+  </si>
+  <si>
     <t>timeframe=1m minimum period</t>
   </si>
   <si>
@@ -654,6 +762,9 @@
     <t>036</t>
   </si>
   <si>
+    <t>TC_R036</t>
+  </si>
+  <si>
     <t>timeframe=1M maximum period</t>
   </si>
   <si>
@@ -669,6 +780,9 @@
     <t>037</t>
   </si>
   <si>
+    <t>TC_R037</t>
+  </si>
+  <si>
     <t>start_ts=0 (epoch time)</t>
   </si>
   <si>
@@ -687,6 +801,9 @@
     <t>038</t>
   </si>
   <si>
+    <t>TC_R038</t>
+  </si>
+  <si>
     <t>end_ts future time</t>
   </si>
   <si>
@@ -705,6 +822,9 @@
     <t>039</t>
   </si>
   <si>
+    <t>TC_R039</t>
+  </si>
+  <si>
     <t>start_ts equals end_ts</t>
   </si>
   <si>
@@ -723,6 +843,9 @@
     <t>040</t>
   </si>
   <si>
+    <t>TC_R040</t>
+  </si>
+  <si>
     <t>Very long instrument_name (500 chars)</t>
   </si>
   <si>
@@ -741,6 +864,9 @@
     <t>041</t>
   </si>
   <si>
+    <t>TC_R041</t>
+  </si>
+  <si>
     <t>Empty instrument_name</t>
   </si>
   <si>
@@ -759,6 +885,9 @@
     <t>042</t>
   </si>
   <si>
+    <t>TC_R042</t>
+  </si>
+  <si>
     <t>count=999999 extreme value</t>
   </si>
   <si>
@@ -777,6 +906,9 @@
     <t>043</t>
   </si>
   <si>
+    <t>TC_R043</t>
+  </si>
+  <si>
     <t>Request timeout</t>
   </si>
   <si>
@@ -795,6 +927,9 @@
     <t>044</t>
   </si>
   <si>
+    <t>TC_R044</t>
+  </si>
+  <si>
     <t>100 concurrent requests</t>
   </si>
   <si>
@@ -810,6 +945,9 @@
     <t>045</t>
   </si>
   <si>
+    <t>TC_R045</t>
+  </si>
+  <si>
     <t>Data consistency: h&gt;=l, o/c in range</t>
   </si>
   <si>
@@ -825,6 +963,9 @@
     <t>046</t>
   </si>
   <si>
+    <t>TC_R046</t>
+  </si>
+  <si>
     <t>Verify timestamp ascending order</t>
   </si>
   <si>
@@ -841,6 +982,9 @@
   </si>
   <si>
     <t>Post-conditions</t>
+  </si>
+  <si>
+    <t>TC_001</t>
   </si>
   <si>
     <t>Subscribe book depth=50 with Delta mode (default recommended)</t>
@@ -877,6 +1021,9 @@
     <t>Most common scenario, highest priority</t>
   </si>
   <si>
+    <t>TC_002</t>
+  </si>
+  <si>
     <t>Subscribe book depth=10 with Delta mode</t>
   </si>
   <si>
@@ -898,6 +1045,9 @@
     <t>Disconnect</t>
   </si>
   <si>
+    <t>TC_003</t>
+  </si>
+  <si>
     <t>Subscribe book depth=50 with Snapshot mode</t>
   </si>
   <si>
@@ -918,6 +1068,9 @@
     <t>Snapshot mode consumes more bandwidth</t>
   </si>
   <si>
+    <t>TC_004</t>
+  </si>
+  <si>
     <t>Subscribe book depth=10 with Snapshot mode</t>
   </si>
   <si>
@@ -934,6 +1087,9 @@
 3. Data integrity correct</t>
   </si>
   <si>
+    <t>TC_005</t>
+  </si>
+  <si>
     <t>Subscribe BTCUSD-PERP trading pair</t>
   </si>
   <si>
@@ -956,6 +1112,9 @@
     <t>Major trading pair test</t>
   </si>
   <si>
+    <t>TC_006</t>
+  </si>
+  <si>
     <t>Subscribe ETHUSD-PERP trading pair</t>
   </si>
   <si>
@@ -974,6 +1133,9 @@
 2. Data streaming normally</t>
   </si>
   <si>
+    <t>TC_007</t>
+  </si>
+  <si>
     <t>Verify Delta mode default 100ms update frequency</t>
   </si>
   <si>
@@ -995,6 +1157,9 @@
     <t>Performance test</t>
   </si>
   <si>
+    <t>TC_008</t>
+  </si>
+  <si>
     <t>Verify Delta mode 10ms high-frequency updates</t>
   </si>
   <si>
@@ -1010,6 +1175,9 @@
   </si>
   <si>
     <t>High-frequency trading scenario</t>
+  </si>
+  <si>
+    <t>TC_009</t>
   </si>
   <si>
     <t>Verify Snapshot mode default 500ms frequency</t>
@@ -1024,6 +1192,9 @@
   </si>
   <si>
     <t>1. Average interval ~500ms±50ms</t>
+  </si>
+  <si>
+    <t>TC_010</t>
   </si>
   <si>
     <t>Verify asks array structure integrity</t>
@@ -1048,6 +1219,9 @@
 6. Prices sorted ascending</t>
   </si>
   <si>
+    <t>TC_011</t>
+  </si>
+  <si>
     <t>Verify bids array structure integrity</t>
   </si>
   <si>
@@ -1062,6 +1236,9 @@
 4. Prices sorted descending (high to low)</t>
   </si>
   <si>
+    <t>TC_012</t>
+  </si>
+  <si>
     <t>Verify response contains correct channel field</t>
   </si>
   <si>
@@ -1074,6 +1251,9 @@
   <si>
     <t>1. Response contains channel field
 2. channel="book"</t>
+  </si>
+  <si>
+    <t>TC_013</t>
   </si>
   <si>
     <t>Verify subscription field format is correct</t>
@@ -1089,6 +1269,9 @@
     <t>1. subscription field exists
 2. Format is "book.{instrument}.{depth}"
 3. Consistent with subscription params</t>
+  </si>
+  <si>
+    <t>TC_014</t>
   </si>
   <si>
     <t>Normal disconnect after subscription</t>
@@ -1112,6 +1295,9 @@
   </si>
   <si>
     <t>Connection closed</t>
+  </si>
+  <si>
+    <t>TC_015</t>
   </si>
   <si>
     <t>Receive multiple messages and verify data consistency</t>
@@ -1135,6 +1321,9 @@
     <t>Data consistency validation</t>
   </si>
   <si>
+    <t>TC_016</t>
+  </si>
+  <si>
     <t>WebSocket available</t>
   </si>
   <si>
@@ -1150,6 +1339,9 @@
     <t>Typical negative case</t>
   </si>
   <si>
+    <t>TC_017</t>
+  </si>
+  <si>
     <t>Non-existent trading pair</t>
   </si>
   <si>
@@ -1159,6 +1351,9 @@
     <t>{}</t>
   </si>
   <si>
+    <t>TC_018</t>
+  </si>
+  <si>
     <t>Invalid depth value 15</t>
   </si>
   <si>
@@ -1171,9 +1366,15 @@
     <t>Parameter validation</t>
   </si>
   <si>
+    <t>TC_019</t>
+  </si>
+  <si>
     <t>depth as string type</t>
   </si>
   <si>
+    <t>TC_020</t>
+  </si>
+  <si>
     <t>Missing instrument_name</t>
   </si>
   <si>
@@ -1183,15 +1384,27 @@
     <t>Required parameter missing</t>
   </si>
   <si>
+    <t>TC_021</t>
+  </si>
+  <si>
     <t>Missing depth</t>
   </si>
   <si>
+    <t>TC_022</t>
+  </si>
+  <si>
     <t>Invalid subscription_type</t>
   </si>
   <si>
+    <t>TC_023</t>
+  </si>
+  <si>
     <t>Invalid update_frequency</t>
   </si>
   <si>
+    <t>TC_024</t>
+  </si>
+  <si>
     <t>Malformed JSON</t>
   </si>
   <si>
@@ -1210,6 +1423,9 @@
     <t>Error tolerance test</t>
   </si>
   <si>
+    <t>TC_025</t>
+  </si>
+  <si>
     <t>method not subscribe</t>
   </si>
   <si>
@@ -1222,6 +1438,9 @@
     <t>Method error</t>
   </si>
   <si>
+    <t>TC_026</t>
+  </si>
+  <si>
     <t>Missing method field</t>
   </si>
   <si>
@@ -1231,9 +1450,15 @@
     <t>Field missing</t>
   </si>
   <si>
+    <t>TC_027</t>
+  </si>
+  <si>
     <t>Missing params field</t>
   </si>
   <si>
+    <t>TC_028</t>
+  </si>
+  <si>
     <t>depth minimum valid value 10</t>
   </si>
   <si>
@@ -1243,6 +1468,9 @@
     <t>{"channels":["book.BTCUSD-PERP.10"]}</t>
   </si>
   <si>
+    <t>TC_029</t>
+  </si>
+  <si>
     <t>depth maximum valid value 50</t>
   </si>
   <si>
@@ -1255,6 +1483,9 @@
     <t>Maximum boundary</t>
   </si>
   <si>
+    <t>TC_030</t>
+  </si>
+  <si>
     <t>depth=9 below minimum</t>
   </si>
   <si>
@@ -1264,27 +1495,48 @@
     <t>Fail</t>
   </si>
   <si>
+    <t>TC_031</t>
+  </si>
+  <si>
     <t>depth=51 above maximum</t>
   </si>
   <si>
     <t>Above maximum</t>
   </si>
   <si>
+    <t>TC_032</t>
+  </si>
+  <si>
     <t>depth=0</t>
   </si>
   <si>
+    <t>TC_033</t>
+  </si>
+  <si>
     <t>depth=-10 negative</t>
   </si>
   <si>
+    <t>TC_034</t>
+  </si>
+  <si>
     <t>Very long instrument_name</t>
   </si>
   <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t>TC_036</t>
+  </si>
+  <si>
     <t>frequency=10ms minimum</t>
   </si>
   <si>
     <t>Minimum frequency</t>
   </si>
   <si>
+    <t>TC_037</t>
+  </si>
+  <si>
     <t>frequency=500ms Snapshot default</t>
   </si>
   <si>
@@ -1294,6 +1546,9 @@
     <t>Snapshot default freq</t>
   </si>
   <si>
+    <t>TC_038</t>
+  </si>
+  <si>
     <t>Connection timeout</t>
   </si>
   <si>
@@ -1306,6 +1561,9 @@
     <t>Timeout exception</t>
   </si>
   <si>
+    <t>TC_039</t>
+  </si>
+  <si>
     <t>Disconnect immediately after subscribe</t>
   </si>
   <si>
@@ -1321,6 +1579,9 @@
     <t>Resource cleanup</t>
   </si>
   <si>
+    <t>TC_040</t>
+  </si>
+  <si>
     <t>Repeated subscriptions</t>
   </si>
   <si>
@@ -1331,6 +1592,9 @@
   </si>
   <si>
     <t>Duplicate subscription</t>
+  </si>
+  <si>
+    <t>TC_041</t>
   </si>
   <si>
     <t>Multiple depth subscriptions</t>
@@ -1355,7 +1619,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,13 +1633,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1846,28 +2103,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1876,118 +2136,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2355,25 +2612,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="30.7692307692308" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="22.9134615384615" customWidth="1"/>
-    <col min="10" max="10" width="35" customWidth="1"/>
-    <col min="11" max="11" width="45" customWidth="1"/>
-    <col min="12" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="30.7692307692308" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="22.9134615384615" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="45" customWidth="1"/>
+    <col min="13" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1" spans="1:15">
+    <row r="1" ht="35" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2419,2167 +2676,2308 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" ht="80" customHeight="1" spans="1:15">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1" spans="1:16">
+      <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" ht="80" customHeight="1" spans="1:15">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1" spans="1:16">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1" spans="1:16">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:16">
+      <c r="A6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1" spans="1:15">
-      <c r="A4" s="3" t="s">
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" spans="1:16">
+      <c r="A7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" spans="1:16">
+      <c r="A8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1" spans="1:16">
+      <c r="A9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1" spans="1:16">
+      <c r="A10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:16">
+      <c r="A11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:16">
+      <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1" spans="1:16">
+      <c r="A13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1" spans="1:16">
+      <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1" spans="1:16">
+      <c r="A15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="1:16">
+      <c r="A16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:16">
+      <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1" spans="1:16">
+      <c r="A21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:16">
+      <c r="A22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" spans="1:16">
+      <c r="A23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1" spans="1:16">
+      <c r="A24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" spans="1:16">
+      <c r="A25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1" spans="1:16">
+      <c r="A26" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1" spans="1:16">
+      <c r="A27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1" spans="1:16">
+      <c r="A28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1" spans="1:16">
+      <c r="A29" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1" spans="1:16">
+      <c r="A30" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1" spans="1:16">
+      <c r="A31" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" spans="1:16">
+      <c r="A32" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1" spans="1:16">
+      <c r="A33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1" spans="1:16">
+      <c r="A34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1" spans="1:16">
+      <c r="A35" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1" spans="1:16">
+      <c r="A36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="L36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1" spans="1:16">
+      <c r="A37" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1" spans="1:16">
+      <c r="A38" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1" spans="1:16">
+      <c r="A39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1" spans="1:16">
+      <c r="A40" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1" spans="1:16">
+      <c r="A41" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1" spans="1:16">
+      <c r="A42" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1" spans="1:16">
+      <c r="A43" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1" spans="1:16">
+      <c r="A44" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="45" ht="80" customHeight="1" spans="1:16">
+      <c r="A45" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" ht="80" customHeight="1" spans="1:16">
+      <c r="A46" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="F46" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1" spans="1:15">
-      <c r="A5" s="3" t="s">
+      <c r="H46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1" spans="1:16">
+      <c r="A47" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="F47" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:15">
-      <c r="A6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" spans="1:15">
-      <c r="A7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1" spans="1:15">
-      <c r="A10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1" spans="1:15">
-      <c r="A11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1" spans="1:15">
-      <c r="A12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1" spans="1:15">
-      <c r="A13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1" spans="1:15">
-      <c r="A15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1" spans="1:15">
-      <c r="A16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1" spans="1:15">
-      <c r="A17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:15">
-      <c r="A18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="1:15">
-      <c r="A19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:15">
-      <c r="A20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1" spans="1:15">
-      <c r="A21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" ht="80" customHeight="1" spans="1:15">
-      <c r="A22" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1" spans="1:15">
-      <c r="A23" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1" spans="1:15">
-      <c r="A24" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1" spans="1:15">
-      <c r="A25" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" ht="80" customHeight="1" spans="1:15">
-      <c r="A26" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1" spans="1:15">
-      <c r="A27" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" ht="80" customHeight="1" spans="1:15">
-      <c r="A28" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" ht="80" customHeight="1" spans="1:15">
-      <c r="A29" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" ht="80" customHeight="1" spans="1:15">
-      <c r="A30" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" ht="80" customHeight="1" spans="1:15">
-      <c r="A31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" ht="80" customHeight="1" spans="1:15">
-      <c r="A32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" ht="80" customHeight="1" spans="1:15">
-      <c r="A33" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" ht="80" customHeight="1" spans="1:15">
-      <c r="A34" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" ht="80" customHeight="1" spans="1:15">
-      <c r="A35" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" ht="80" customHeight="1" spans="1:15">
-      <c r="A36" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" ht="80" customHeight="1" spans="1:15">
-      <c r="A37" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" ht="80" customHeight="1" spans="1:15">
-      <c r="A38" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" ht="80" customHeight="1" spans="1:15">
-      <c r="A39" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" ht="80" customHeight="1" spans="1:15">
-      <c r="A40" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="41" ht="80" customHeight="1" spans="1:15">
-      <c r="A41" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="42" ht="80" customHeight="1" spans="1:15">
-      <c r="A42" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="43" ht="80" customHeight="1" spans="1:15">
-      <c r="A43" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44" ht="80" customHeight="1" spans="1:15">
-      <c r="A44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="45" ht="80" customHeight="1" spans="1:15">
-      <c r="A45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" ht="80" customHeight="1" spans="1:15">
-      <c r="A46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="47" ht="80" customHeight="1" spans="1:15">
-      <c r="A47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>26</v>
+        <v>315</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>269</v>
+        <v>30</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4591,25 +4989,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="45" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1" spans="1:14">
+    <row r="1" ht="35" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4626,7 +5024,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>8</v>
@@ -4638,10 +5036,10 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>270</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>11</v>
+        <v>317</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>12</v>
@@ -4652,1809 +5050,1935 @@
       <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" ht="80" customHeight="1" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1" spans="1:15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>26</v>
+        <v>325</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="3" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1" spans="1:15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1" spans="1:15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>272</v>
+        <v>334</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1" spans="1:15">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" spans="1:15">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>299</v>
+        <v>351</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>283</v>
+        <v>356</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" spans="1:15">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>272</v>
+        <v>358</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>283</v>
+        <v>362</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1" spans="1:15">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>272</v>
+        <v>365</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>283</v>
+        <v>368</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1" spans="1:15">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>272</v>
+        <v>371</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:15">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>272</v>
+        <v>376</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>323</v>
+        <v>379</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:15">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>272</v>
+        <v>382</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1" spans="1:15">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>272</v>
+        <v>386</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>330</v>
+        <v>379</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>283</v>
+        <v>389</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1" spans="1:15">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>272</v>
+        <v>391</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="L14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1" spans="1:15">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>272</v>
+        <v>396</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="1:15">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>341</v>
+        <v>402</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>272</v>
+        <v>403</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>343</v>
+        <v>404</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>296</v>
+        <v>405</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>283</v>
+        <v>406</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>408</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>151</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1" spans="1:15">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>272</v>
+        <v>415</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1" spans="1:15">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>272</v>
+        <v>419</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>356</v>
+        <v>420</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>142</v>
+        <v>421</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:15">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>358</v>
+        <v>423</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>272</v>
+        <v>424</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>151</v>
+        <v>409</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>353</v>
+        <v>176</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1" spans="1:15">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>272</v>
+        <v>426</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>353</v>
+        <v>427</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>283</v>
+        <v>428</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:15">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>272</v>
+        <v>430</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>353</v>
+        <v>427</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>283</v>
+        <v>428</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" spans="1:15">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>363</v>
+        <v>431</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>272</v>
+        <v>432</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>409</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>142</v>
+        <v>417</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1" spans="1:15">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>364</v>
+        <v>433</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>272</v>
+        <v>434</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>346</v>
+        <v>144</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>131</v>
+        <v>409</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>142</v>
+        <v>417</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" spans="1:15">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>272</v>
+        <v>436</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>366</v>
+        <v>144</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>367</v>
+        <v>437</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>369</v>
+        <v>439</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>283</v>
+        <v>440</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="26" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1" spans="1:15">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>272</v>
+        <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>366</v>
+        <v>144</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>283</v>
+        <v>446</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1" spans="1:15">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>272</v>
+        <v>448</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>366</v>
+        <v>144</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>353</v>
+        <v>449</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>283</v>
+        <v>450</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1" spans="1:15">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>378</v>
+        <v>451</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>272</v>
+        <v>452</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>366</v>
+        <v>144</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>353</v>
+        <v>449</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>283</v>
+        <v>450</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1" spans="1:15">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>379</v>
+        <v>453</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>272</v>
+        <v>454</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>381</v>
+        <v>455</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>63</v>
+        <v>456</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="30" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1" spans="1:15">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>272</v>
+        <v>458</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>63</v>
+        <v>460</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="31" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1" spans="1:15">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>353</v>
+        <v>464</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="32" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" spans="1:15">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>389</v>
+        <v>466</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>353</v>
+        <v>468</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="33" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1" spans="1:15">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>391</v>
+        <v>469</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>272</v>
+        <v>470</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>189</v>
+        <v>409</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1" spans="1:15">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>392</v>
+        <v>471</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>272</v>
+        <v>472</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>353</v>
+        <v>144</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1" spans="1:15">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>393</v>
+        <v>473</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>272</v>
+        <v>474</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>232</v>
+        <v>409</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>234</v>
+        <v>417</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="36" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1" spans="1:15">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>237</v>
+        <v>475</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>238</v>
+        <v>409</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>240</v>
+        <v>417</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O36" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" ht="80" customHeight="1" spans="1:14">
+    </row>
+    <row r="37" ht="80" customHeight="1" spans="1:15">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>272</v>
+        <v>477</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>353</v>
+        <v>478</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>63</v>
+        <v>417</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="38" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1" spans="1:15">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>396</v>
+        <v>479</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>272</v>
+        <v>480</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>353</v>
+        <v>481</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>63</v>
+        <v>417</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="39" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1" spans="1:15">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>399</v>
+        <v>483</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>251</v>
+        <v>485</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>401</v>
+        <v>295</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>402</v>
+        <v>486</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>400</v>
+        <v>487</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>26</v>
+        <v>485</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="40" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1" spans="1:15">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>403</v>
+        <v>488</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>272</v>
+        <v>489</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>366</v>
+        <v>294</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>353</v>
+        <v>490</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>406</v>
+        <v>491</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>26</v>
+        <v>492</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="41" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1" spans="1:15">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>272</v>
+        <v>495</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>366</v>
+        <v>294</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>353</v>
+        <v>496</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>283</v>
+        <v>497</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="42" ht="80" customHeight="1" spans="1:14">
+        <v>30</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1" spans="1:15">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>412</v>
+        <v>499</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>272</v>
+        <v>500</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>366</v>
+        <v>294</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>353</v>
+        <v>501</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>283</v>
+        <v>502</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>415</v>
+        <v>30</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>
